--- a/technology_surveys/024_digital_health_adoption_strategy_evaluation_form--technology_surveys.xlsx
+++ b/technology_surveys/024_digital_health_adoption_strategy_evaluation_form--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'ceo/owner',_'value':_'ceo/owner'}</t>
+          <t>ceo/owner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'CEO/Owner', 'value': 'CEO/Owner'}</t>
+          <t>CEO/Owner</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'project_manager',_'value':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Project Manager', 'value': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'it_director',_'value':_'it_director'}</t>
+          <t>it_director</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'IT Director', 'value': 'IT Director'}</t>
+          <t>IT Director</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_10',_'value':_'less_than_10'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 10', 'value': 'Less than 10'}</t>
+          <t>Less than 10</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'10-50',_'value':_'10-50'}</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '10-50', 'value': '10-50'}</t>
+          <t>10-50</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'51-100',_'value':_'51-100'}</t>
+          <t>51-100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '51-100', 'value': '51-100'}</t>
+          <t>51-100</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'more_than_100',_'value':_'more_than_100'}</t>
+          <t>more_than_100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'More than 100', 'value': 'More than 100'}</t>
+          <t>More than 100</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_started',_'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not started', 'value': 'Not started'}</t>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In progress', 'value': 'In progress'}</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'increasing_efficiency',_'value':_'increasing_efficiency'}</t>
+          <t>increasing_efficiency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Increasing efficiency', 'value': 'Increasing efficiency'}</t>
+          <t>Increasing efficiency</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cost_savings',_'value':_'cost_savings'}</t>
+          <t>cost_savings</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cost savings', 'value': 'Cost savings'}</t>
+          <t>Cost savings</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'improved_customer_satisfaction',_'value':_'improved_customer_satisfaction'}</t>
+          <t>improved_customer_satisfaction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Improved customer satisfaction', 'value': 'Improved customer satisfaction'}</t>
+          <t>Improved customer satisfaction</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'improved_patient_satisfaction',_'value':_'improved_patient_satisfaction'}</t>
+          <t>improved_patient_satisfaction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Improved patient satisfaction', 'value': 'Improved patient satisfaction'}</t>
+          <t>Improved patient satisfaction</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lack_of_resources',_'value':_'lack_of_resources'}</t>
+          <t>lack_of_resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Lack of resources', 'value': 'Lack of resources'}</t>
+          <t>Lack of resources</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'change_management',_'value':_'change_management'}</t>
+          <t>change_management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Change management', 'value': 'Change management'}</t>
+          <t>Change management</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'data_security_and_privacy_concerns',_'value':_'data_security_and_privacy_concerns'}</t>
+          <t>data_security_and_privacy_concerns</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Data security and privacy concerns', 'value': 'Data security and privacy concerns'}</t>
+          <t>Data security and privacy concerns</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)',_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)', 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basic',_'value':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Basic', 'value': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'intermediate',_'value':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Intermediate', 'value': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'advanced',_'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Advanced', 'value': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'frequently',_'value':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Frequently', 'value': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally',_'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally', 'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'conferences',_'value':_'conferences'}</t>
+          <t>conferences</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Conferences', 'value': 'Conferences'}</t>
+          <t>Conferences</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'online_articles',_'value':_'online_articles'}</t>
+          <t>online_articles</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Online articles', 'value': 'Online articles'}</t>
+          <t>Online articles</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'social_media',_'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Social media', 'value': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'podcasts',_'value':_'podcasts'}</t>
+          <t>podcasts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Podcasts', 'value': 'Podcasts'}</t>
+          <t>Podcasts</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'webinars',_'value':_'webinars'}</t>
+          <t>webinars</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Webinars', 'value': 'Webinars'}</t>
+          <t>Webinars</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'books',_'value':_'books'}</t>
+          <t>books</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Books', 'value': 'Books'}</t>
+          <t>Books</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'other_(please_specify)',_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Other (please specify)', 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Often', 'value': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometimes', 'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
